--- a/data/trans_dic/P36BPD13_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,68; 93,8</t>
+          <t>88,55; 93,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,89; 94,32</t>
+          <t>90,77; 94,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,48; 93,51</t>
+          <t>90,42; 93,51</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,3; 94,7</t>
+          <t>86,27; 94,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,22; 91,74</t>
+          <t>88,35; 91,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,04; 93,32</t>
+          <t>87,93; 93,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,74; 76,4</t>
+          <t>68,53; 76,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,19; 93,03</t>
+          <t>82,25; 94,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,19; 87,73</t>
+          <t>77,13; 87,45</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>82,29; 87,48</t>
+          <t>81,93; 87,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,37; 90,22</t>
+          <t>85,09; 89,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,4; 87,89</t>
+          <t>84,49; 88,0</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,51</t>
+          <t>83,39; 88,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,73; 90,99</t>
+          <t>87,72; 90,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,04; 89,2</t>
+          <t>86,06; 88,86</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>561183; 593540</t>
+          <t>560328; 592050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>609329; 632298</t>
+          <t>608522; 631677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1179096; 1218569</t>
+          <t>1178387; 1218542</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1025407; 1125171</t>
+          <t>1025045; 1125848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>840233; 873793</t>
+          <t>841533; 873504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1884586; 1997758</t>
+          <t>1882270; 1994763</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>481026; 534693</t>
+          <t>479615; 536416</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>761911; 862455</t>
+          <t>762467; 873141</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1255705; 1427284</t>
+          <t>1254752; 1422775</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>756257; 803942</t>
+          <t>752944; 802346</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926691; 979284</t>
+          <t>923638; 975436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1691733; 1761856</t>
+          <t>1693595; 1763950</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2875657; 3044662</t>
+          <t>2868463; 3037284</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3189337; 3307672</t>
+          <t>3188872; 3303712</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6087588; 6310817</t>
+          <t>6088937; 6286971</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD13_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,55; 93,56</t>
+          <t>88,67; 93,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>90,77; 94,23</t>
+          <t>90,62; 94,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,42; 93,51</t>
+          <t>90,4; 93,44</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,27; 94,75</t>
+          <t>85,2; 90,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>88,35; 91,71</t>
+          <t>88,4; 91,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87,93; 93,18</t>
+          <t>87,36; 90,19</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>68,53; 76,65</t>
+          <t>70,58; 77,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,25; 94,18</t>
+          <t>80,1; 84,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,13; 87,45</t>
+          <t>76,08; 80,52</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,56%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,3</t>
+          <t>82,14; 87,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,09; 89,86</t>
+          <t>84,2; 88,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,49; 88,0</t>
+          <t>83,93; 87,03</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>83,39; 88,3</t>
+          <t>83,14; 85,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>87,72; 90,88</t>
+          <t>86,82; 88,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86,06; 88,86</t>
+          <t>85,35; 87,03</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>579029</t>
+          <t>629152</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>621396</t>
+          <t>674188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1200426</t>
+          <t>1303341</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>560328; 592050</t>
+          <t>609950; 643058</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>608522; 631677</t>
+          <t>659400; 684769</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1178387; 1218542</t>
+          <t>1279612; 1322603</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1067809</t>
+          <t>914199</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>858498</t>
+          <t>959056</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1926307</t>
+          <t>1873255</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1025045; 1125848</t>
+          <t>889390; 939480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>841533; 873504</t>
+          <t>940819; 975384</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1882270; 1994763</t>
+          <t>1841651; 1901444</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>509461</t>
+          <t>590782</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>805567</t>
+          <t>663103</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1315028</t>
+          <t>1253886</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>479615; 536416</t>
+          <t>562533; 617240</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>762467; 873141</t>
+          <t>644388; 683595</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1254752; 1422775</t>
+          <t>1218291; 1289433</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>780306</t>
+          <t>834243</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>948196</t>
+          <t>955352</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1728503</t>
+          <t>1789594</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>752944; 802346</t>
+          <t>807279; 857191</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>923638; 975436</t>
+          <t>933552; 975711</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1693595; 1763950</t>
+          <t>1755342; 1820240</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2868463; 3037284</t>
+          <t>2919385; 3018999</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3188872; 3303712</t>
+          <t>3216731; 3288283</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6088937; 6286971</t>
+          <t>6159518; 6280462</t>
         </is>
       </c>
     </row>
